--- a/Unity/Assets/Config/Excel/WaveConfig.xlsx
+++ b/Unity/Assets/Config/Excel/WaveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="22185" windowHeight="9555"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -38,6 +38,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>HaveBoss</t>
+  </si>
+  <si>
     <t>MonsterBatchIds</t>
   </si>
   <si>
@@ -50,6 +53,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>(array#sep=,),int</t>
   </si>
   <si>
@@ -59,12 +65,18 @@
     <t>关卡名称</t>
   </si>
   <si>
+    <t>有Boss</t>
+  </si>
+  <si>
     <t>怪物批次 Id</t>
   </si>
   <si>
     <t>关卡1-1第1波</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>1010101</t>
   </si>
   <si>
@@ -75,6 +87,9 @@
   </si>
   <si>
     <t>关卡1-1第3波</t>
+  </si>
+  <si>
+    <t>true</t>
   </si>
   <si>
     <t>1010301</t>
@@ -1125,17 +1140,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="7" outlineLevelCol="3"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
-    <col min="2" max="3" width="17.875" style="2"/>
-    <col min="4" max="4" width="33" style="2" customWidth="1"/>
-    <col min="5" max="16381" width="17.875" style="2"/>
-    <col min="16382" max="16384" width="17.875" style="3"/>
+    <col min="2" max="2" width="17.875" style="2"/>
+    <col min="3" max="4" width="18" style="2" customWidth="1"/>
+    <col min="5" max="5" width="33" style="2" customWidth="1"/>
+    <col min="6" max="16382" width="17.875" style="2"/>
+    <col min="16383" max="16384" width="17.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:4">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1148,88 +1164,112 @@
       <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:4">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:4">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:4">
+    <row r="4" customHeight="1" spans="2:5">
       <c r="B4" s="2">
         <v>10101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:4">
+    <row r="5" customHeight="1" spans="2:5">
       <c r="B5" s="2">
         <v>10102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:4">
+    <row r="6" customHeight="1" spans="2:5">
       <c r="B6" s="2">
         <v>10103</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="2:5">
+      <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>16</v>
+      <c r="E7" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="2:4">
-      <c r="B7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="2:4">
+    <row r="8" customHeight="1" spans="2:5">
       <c r="B8" s="2">
         <v>20102</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>21</v>
+      <c r="E8" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/WaveConfig.xlsx
+++ b/Unity/Assets/Config/Excel/WaveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -71,13 +71,16 @@
     <t>怪物批次 Id</t>
   </si>
   <si>
+    <t>10101</t>
+  </si>
+  <si>
     <t>关卡1-1第1波</t>
   </si>
   <si>
     <t>false</t>
   </si>
   <si>
-    <t>1010101</t>
+    <t>1010101,1010102</t>
   </si>
   <si>
     <t>关卡1-1第2波</t>
@@ -93,6 +96,24 @@
   </si>
   <si>
     <t>1010301</t>
+  </si>
+  <si>
+    <t>10201</t>
+  </si>
+  <si>
+    <t>关卡1-2第1波</t>
+  </si>
+  <si>
+    <t>10202</t>
+  </si>
+  <si>
+    <t>关卡1-2第2波</t>
+  </si>
+  <si>
+    <t>10203</t>
+  </si>
+  <si>
+    <t>关卡1-2第3波</t>
   </si>
   <si>
     <t>20101</t>
@@ -1140,8 +1161,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="7" outlineLevelCol="4"/>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="17.875" style="2"/>
@@ -1203,17 +1224,17 @@
       </c>
     </row>
     <row r="4" customHeight="1" spans="2:5">
-      <c r="B4" s="2">
-        <v>10101</v>
+      <c r="B4" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="2:5">
@@ -1221,13 +1242,13 @@
         <v>10102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="2:5">
@@ -1235,41 +1256,83 @@
         <v>10103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="2:5">
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="2:5">
-      <c r="B8" s="2">
+      <c r="B8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="2:5">
+      <c r="B9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="2:5">
+      <c r="B10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="2:5">
+      <c r="B11" s="2">
         <v>20102</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
+      <c r="C11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/WaveConfig.xlsx
+++ b/Unity/Assets/Config/Excel/WaveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22185" windowHeight="9555"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
   <si>
     <t>##var</t>
   </si>
@@ -41,7 +41,7 @@
     <t>HaveBoss</t>
   </si>
   <si>
-    <t>MonsterBatchIds</t>
+    <t>MonsterSpawnInfos</t>
   </si>
   <si>
     <t>##type</t>
@@ -56,7 +56,7 @@
     <t>bool</t>
   </si>
   <si>
-    <t>(array#sep=,),int</t>
+    <t>(array#sep=@),monsterSpawnInfo</t>
   </si>
   <si>
     <t>##</t>
@@ -80,22 +80,40 @@
     <t>false</t>
   </si>
   <si>
-    <t>1010101,1010102</t>
+    <t>0.5;-5,5;10000001@2.5;5,5;10000002</t>
   </si>
   <si>
     <t>关卡1-1第2波</t>
   </si>
   <si>
-    <t>1010201,1010202</t>
+    <t>10103</t>
   </si>
   <si>
     <t>关卡1-1第3波</t>
   </si>
   <si>
+    <t>10104</t>
+  </si>
+  <si>
+    <t>关卡1-1第4波</t>
+  </si>
+  <si>
+    <t>10105</t>
+  </si>
+  <si>
+    <t>关卡1-1第5波</t>
+  </si>
+  <si>
+    <t>10106</t>
+  </si>
+  <si>
+    <t>关卡1-1Boss</t>
+  </si>
+  <si>
     <t>true</t>
   </si>
   <si>
-    <t>1010301</t>
+    <t>0.5;-5,5;10000003</t>
   </si>
   <si>
     <t>10201</t>
@@ -116,19 +134,22 @@
     <t>关卡1-2第3波</t>
   </si>
   <si>
-    <t>20101</t>
-  </si>
-  <si>
-    <t>关卡2-1第1波</t>
-  </si>
-  <si>
-    <t>2010101</t>
-  </si>
-  <si>
-    <t>关卡2-1第2波</t>
-  </si>
-  <si>
-    <t>2010201</t>
+    <t>10204</t>
+  </si>
+  <si>
+    <t>关卡1-2第4波</t>
+  </si>
+  <si>
+    <t>10205</t>
+  </si>
+  <si>
+    <t>关卡1-2第5波</t>
+  </si>
+  <si>
+    <t>10206</t>
+  </si>
+  <si>
+    <t>关卡1-2Boss</t>
   </si>
 </sst>
 </file>
@@ -1161,13 +1182,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="17.875" style="2"/>
     <col min="3" max="4" width="18" style="2" customWidth="1"/>
-    <col min="5" max="5" width="33" style="2" customWidth="1"/>
+    <col min="5" max="5" width="106.75" style="2" customWidth="1"/>
     <col min="6" max="16382" width="17.875" style="2"/>
     <col min="16383" max="16384" width="17.875" style="3"/>
   </cols>
@@ -1248,29 +1269,29 @@
         <v>16</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="2:5">
-      <c r="B6" s="2">
-        <v>10103</v>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="2:5">
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>16</v>
@@ -1281,30 +1302,30 @@
     </row>
     <row r="8" customHeight="1" spans="2:5">
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="2:5">
       <c r="B9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="2:5">
@@ -1318,21 +1339,77 @@
         <v>16</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="2:5">
-      <c r="B11" s="2">
-        <v>20102</v>
+      <c r="B11" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="2:5">
+      <c r="B12" s="2" t="s">
         <v>33</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="2:5">
+      <c r="B13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="2:5">
+      <c r="B14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="2:5">
+      <c r="B15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/WaveConfig.xlsx
+++ b/Unity/Assets/Config/Excel/WaveConfig.xlsx
@@ -68,7 +68,7 @@
     <t>有Boss</t>
   </si>
   <si>
-    <t>怪物批次 Id</t>
+    <t>怪物生成</t>
   </si>
   <si>
     <t>10101</t>

--- a/Unity/Assets/Config/Excel/WaveConfig.xlsx
+++ b/Unity/Assets/Config/Excel/WaveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="46">
   <si>
     <t>##var</t>
   </si>
@@ -41,6 +41,9 @@
     <t>HaveBoss</t>
   </si>
   <si>
+    <t>PlayerSpawnPosition</t>
+  </si>
+  <si>
     <t>MonsterSpawnInfos</t>
   </si>
   <si>
@@ -56,6 +59,9 @@
     <t>bool</t>
   </si>
   <si>
+    <t>vector2</t>
+  </si>
+  <si>
     <t>(array#sep=@),monsterSpawnInfo</t>
   </si>
   <si>
@@ -68,6 +74,9 @@
     <t>有Boss</t>
   </si>
   <si>
+    <t>玩家出生点</t>
+  </si>
+  <si>
     <t>怪物生成</t>
   </si>
   <si>
@@ -80,6 +89,9 @@
     <t>false</t>
   </si>
   <si>
+    <t>0,0</t>
+  </si>
+  <si>
     <t>0.5;-5,5;10000001@2.5;5,5;10000002</t>
   </si>
   <si>
@@ -111,6 +123,9 @@
   </si>
   <si>
     <t>true</t>
+  </si>
+  <si>
+    <t>500,-20</t>
   </si>
   <si>
     <t>0.5;-5,5;10000003</t>
@@ -1182,18 +1197,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelCol="4"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="17.875" style="2"/>
     <col min="3" max="4" width="18" style="2" customWidth="1"/>
-    <col min="5" max="5" width="106.75" style="2" customWidth="1"/>
-    <col min="6" max="16382" width="17.875" style="2"/>
-    <col min="16383" max="16384" width="17.875" style="3"/>
+    <col min="5" max="5" width="19.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="106.75" style="2" customWidth="1"/>
+    <col min="7" max="16383" width="17.875" style="2"/>
+    <col min="16384" max="16384" width="17.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1209,207 +1225,252 @@
       <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:5">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="2:5">
+    <row r="4" customHeight="1" spans="2:6">
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="2:5">
+    <row r="5" customHeight="1" spans="2:6">
       <c r="B5" s="2">
         <v>10102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="2:5">
+    <row r="6" customHeight="1" spans="2:6">
       <c r="B6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>17</v>
+      <c r="F6" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="2:5">
+    <row r="7" customHeight="1" spans="2:6">
       <c r="B7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>17</v>
-      </c>
     </row>
-    <row r="8" customHeight="1" spans="2:5">
+    <row r="8" customHeight="1" spans="2:6">
       <c r="B8" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="2:5">
+    <row r="9" customHeight="1" spans="2:6">
       <c r="B9" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="2:5">
+    <row r="10" customHeight="1" spans="2:6">
       <c r="B10" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="2:5">
+    <row r="11" customHeight="1" spans="2:6">
       <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="2:6">
+      <c r="B12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="2:6">
+      <c r="B13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="2:6">
+      <c r="B14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="2:6">
+      <c r="B15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="2:5">
-      <c r="B12" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="2:5">
-      <c r="B13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="2:5">
-      <c r="B14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="2:5">
-      <c r="B15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/WaveConfig.xlsx
+++ b/Unity/Assets/Config/Excel/WaveConfig.xlsx
@@ -62,7 +62,7 @@
     <t>vector2</t>
   </si>
   <si>
-    <t>(array#sep=@),monsterSpawnInfo</t>
+    <t>(array#sep=@),MonsterSpawnInfo</t>
   </si>
   <si>
     <t>##</t>

--- a/Unity/Assets/Config/Excel/WaveConfig.xlsx
+++ b/Unity/Assets/Config/Excel/WaveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="27945" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="60">
   <si>
     <t>##var</t>
   </si>
@@ -92,12 +92,15 @@
     <t>0,0</t>
   </si>
   <si>
+    <t>2;-5,5;10000001@2.5;5,5;10000002</t>
+  </si>
+  <si>
+    <t>关卡1-1第2波</t>
+  </si>
+  <si>
     <t>0.5;-5,5;10000001@2.5;5,5;10000002</t>
   </si>
   <si>
-    <t>关卡1-1第2波</t>
-  </si>
-  <si>
     <t>10103</t>
   </si>
   <si>
@@ -128,43 +131,82 @@
     <t>500,-20</t>
   </si>
   <si>
+    <t>2;-5,5;10000003</t>
+  </si>
+  <si>
+    <t>10201</t>
+  </si>
+  <si>
+    <t>关卡1-2第1波</t>
+  </si>
+  <si>
+    <t>10202</t>
+  </si>
+  <si>
+    <t>关卡1-2第2波</t>
+  </si>
+  <si>
+    <t>10203</t>
+  </si>
+  <si>
+    <t>关卡1-2第3波</t>
+  </si>
+  <si>
+    <t>10204</t>
+  </si>
+  <si>
+    <t>关卡1-2第4波</t>
+  </si>
+  <si>
+    <t>10205</t>
+  </si>
+  <si>
+    <t>关卡1-2第5波</t>
+  </si>
+  <si>
+    <t>10206</t>
+  </si>
+  <si>
+    <t>关卡1-2Boss</t>
+  </si>
+  <si>
     <t>0.5;-5,5;10000003</t>
   </si>
   <si>
-    <t>10201</t>
-  </si>
-  <si>
-    <t>关卡1-2第1波</t>
-  </si>
-  <si>
-    <t>10202</t>
-  </si>
-  <si>
-    <t>关卡1-2第2波</t>
-  </si>
-  <si>
-    <t>10203</t>
-  </si>
-  <si>
-    <t>关卡1-2第3波</t>
-  </si>
-  <si>
-    <t>10204</t>
-  </si>
-  <si>
-    <t>关卡1-2第4波</t>
-  </si>
-  <si>
-    <t>10205</t>
-  </si>
-  <si>
-    <t>关卡1-2第5波</t>
-  </si>
-  <si>
-    <t>10206</t>
-  </si>
-  <si>
-    <t>关卡1-2Boss</t>
+    <t>20101</t>
+  </si>
+  <si>
+    <t>关卡2-1第1波</t>
+  </si>
+  <si>
+    <t>20102</t>
+  </si>
+  <si>
+    <t>关卡2-1第2波</t>
+  </si>
+  <si>
+    <t>20103</t>
+  </si>
+  <si>
+    <t>关卡2-1第3波</t>
+  </si>
+  <si>
+    <t>20104</t>
+  </si>
+  <si>
+    <t>关卡2-1第4波</t>
+  </si>
+  <si>
+    <t>20105</t>
+  </si>
+  <si>
+    <t>关卡2-1第5波</t>
+  </si>
+  <si>
+    <t>20106</t>
+  </si>
+  <si>
+    <t>关卡2-1Boss</t>
   </si>
 </sst>
 </file>
@@ -1197,7 +1239,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultColWidth="17.875" defaultRowHeight="20.1" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="10.875" style="2" customWidth="1"/>
@@ -1300,15 +1342,15 @@
         <v>20</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="2:6">
       <c r="B6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>19</v>
@@ -1317,15 +1359,15 @@
         <v>20</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="2:6">
       <c r="B7" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>19</v>
@@ -1334,15 +1376,15 @@
         <v>20</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="2:6">
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>19</v>
@@ -1351,32 +1393,32 @@
         <v>20</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="2:6">
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="2:6">
       <c r="B10" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>19</v>
@@ -1385,15 +1427,15 @@
         <v>20</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="2:6">
       <c r="B11" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>19</v>
@@ -1402,15 +1444,15 @@
         <v>20</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="2:6">
       <c r="B12" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>19</v>
@@ -1419,15 +1461,15 @@
         <v>20</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="2:6">
       <c r="B13" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>19</v>
@@ -1436,15 +1478,15 @@
         <v>20</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="2:6">
       <c r="B14" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>19</v>
@@ -1453,24 +1495,126 @@
         <v>20</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="2:6">
       <c r="B15" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="2:6">
+      <c r="B16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="2:6">
+      <c r="B17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="2:6">
+      <c r="B18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="2:6">
+      <c r="B19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="2:6">
+      <c r="B20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="2:6">
+      <c r="B21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="E21" s="2" t="s">
         <v>33</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/WaveConfig.xlsx
+++ b/Unity/Assets/Config/Excel/WaveConfig.xlsx
@@ -128,7 +128,7 @@
     <t>true</t>
   </si>
   <si>
-    <t>500,-20</t>
+    <t>500,0</t>
   </si>
   <si>
     <t>2;-5,5;10000003</t>

--- a/Unity/Assets/Config/Excel/WaveConfig.xlsx
+++ b/Unity/Assets/Config/Excel/WaveConfig.xlsx
@@ -92,13 +92,13 @@
     <t>0,0</t>
   </si>
   <si>
-    <t>2;-5,5;10000001@2.5;5,5;10000002</t>
+    <t>2;-5,50;10000001@2.5;5,50;10000002</t>
   </si>
   <si>
     <t>关卡1-1第2波</t>
   </si>
   <si>
-    <t>0.5;-5,5;10000001@2.5;5,5;10000002</t>
+    <t>0.5;-5,50;10000001@2.5;5,50;10000002</t>
   </si>
   <si>
     <t>10103</t>

--- a/Unity/Assets/Config/Excel/WaveConfig.xlsx
+++ b/Unity/Assets/Config/Excel/WaveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12960"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="61">
   <si>
     <t>##var</t>
   </si>
@@ -92,91 +92,94 @@
     <t>0,0</t>
   </si>
   <si>
+    <t>2;-5,50;10000001@2;5,50;10000002@2;0,50;10000002@2.2;5,50;10000002@2.2;2,50;10000002@2.4;2,50;10000002</t>
+  </si>
+  <si>
+    <t>关卡1-1第2波</t>
+  </si>
+  <si>
+    <t>10103</t>
+  </si>
+  <si>
+    <t>关卡1-1第3波</t>
+  </si>
+  <si>
+    <t>10104</t>
+  </si>
+  <si>
+    <t>关卡1-1第4波</t>
+  </si>
+  <si>
+    <t>10105</t>
+  </si>
+  <si>
+    <t>关卡1-1第5波</t>
+  </si>
+  <si>
+    <t>10106</t>
+  </si>
+  <si>
+    <t>关卡1-1Boss</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>500,0</t>
+  </si>
+  <si>
+    <t>2;-5,5;10000003</t>
+  </si>
+  <si>
+    <t>10201</t>
+  </si>
+  <si>
+    <t>关卡1-2第1波</t>
+  </si>
+  <si>
+    <t>0.5;-5,50;10000001@2.5;5,50;10000002</t>
+  </si>
+  <si>
+    <t>10202</t>
+  </si>
+  <si>
+    <t>关卡1-2第2波</t>
+  </si>
+  <si>
+    <t>10203</t>
+  </si>
+  <si>
+    <t>关卡1-2第3波</t>
+  </si>
+  <si>
+    <t>10204</t>
+  </si>
+  <si>
+    <t>关卡1-2第4波</t>
+  </si>
+  <si>
+    <t>10205</t>
+  </si>
+  <si>
+    <t>关卡1-2第5波</t>
+  </si>
+  <si>
+    <t>10206</t>
+  </si>
+  <si>
+    <t>关卡1-2Boss</t>
+  </si>
+  <si>
+    <t>0.5;-5,5;10000003</t>
+  </si>
+  <si>
+    <t>20101</t>
+  </si>
+  <si>
+    <t>关卡2-1第1波</t>
+  </si>
+  <si>
     <t>2;-5,50;10000001@2.5;5,50;10000002</t>
-  </si>
-  <si>
-    <t>关卡1-1第2波</t>
-  </si>
-  <si>
-    <t>0.5;-5,50;10000001@2.5;5,50;10000002</t>
-  </si>
-  <si>
-    <t>10103</t>
-  </si>
-  <si>
-    <t>关卡1-1第3波</t>
-  </si>
-  <si>
-    <t>10104</t>
-  </si>
-  <si>
-    <t>关卡1-1第4波</t>
-  </si>
-  <si>
-    <t>10105</t>
-  </si>
-  <si>
-    <t>关卡1-1第5波</t>
-  </si>
-  <si>
-    <t>10106</t>
-  </si>
-  <si>
-    <t>关卡1-1Boss</t>
-  </si>
-  <si>
-    <t>true</t>
-  </si>
-  <si>
-    <t>500,0</t>
-  </si>
-  <si>
-    <t>2;-5,5;10000003</t>
-  </si>
-  <si>
-    <t>10201</t>
-  </si>
-  <si>
-    <t>关卡1-2第1波</t>
-  </si>
-  <si>
-    <t>10202</t>
-  </si>
-  <si>
-    <t>关卡1-2第2波</t>
-  </si>
-  <si>
-    <t>10203</t>
-  </si>
-  <si>
-    <t>关卡1-2第3波</t>
-  </si>
-  <si>
-    <t>10204</t>
-  </si>
-  <si>
-    <t>关卡1-2第4波</t>
-  </si>
-  <si>
-    <t>10205</t>
-  </si>
-  <si>
-    <t>关卡1-2第5波</t>
-  </si>
-  <si>
-    <t>10206</t>
-  </si>
-  <si>
-    <t>关卡1-2Boss</t>
-  </si>
-  <si>
-    <t>0.5;-5,5;10000003</t>
-  </si>
-  <si>
-    <t>20101</t>
-  </si>
-  <si>
-    <t>关卡2-1第1波</t>
   </si>
   <si>
     <t>20102</t>
@@ -1246,7 +1249,7 @@
     <col min="2" max="2" width="17.875" style="2"/>
     <col min="3" max="4" width="18" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="106.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="129.25" style="2" customWidth="1"/>
     <col min="7" max="16383" width="17.875" style="2"/>
     <col min="16384" max="16384" width="17.875" style="3"/>
   </cols>
@@ -1342,15 +1345,15 @@
         <v>20</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="2:6">
       <c r="B6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>19</v>
@@ -1359,15 +1362,15 @@
         <v>20</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="2:6">
       <c r="B7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>19</v>
@@ -1376,15 +1379,15 @@
         <v>20</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="2:6">
       <c r="B8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>19</v>
@@ -1393,32 +1396,32 @@
         <v>20</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="2:6">
       <c r="B9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="2:6">
       <c r="B10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>19</v>
@@ -1427,7 +1430,7 @@
         <v>20</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="2:6">
@@ -1444,7 +1447,7 @@
         <v>20</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="2:6">
@@ -1461,7 +1464,7 @@
         <v>20</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="2:6">
@@ -1478,7 +1481,7 @@
         <v>20</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="2:6">
@@ -1495,7 +1498,7 @@
         <v>20</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="2:6">
@@ -1506,10 +1509,10 @@
         <v>46</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>47</v>
@@ -1529,15 +1532,15 @@
         <v>20</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:6">
       <c r="B17" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>19</v>
@@ -1546,15 +1549,15 @@
         <v>20</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:6">
       <c r="B18" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>19</v>
@@ -1563,15 +1566,15 @@
         <v>20</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:6">
       <c r="B19" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>19</v>
@@ -1580,15 +1583,15 @@
         <v>20</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:6">
       <c r="B20" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>19</v>
@@ -1597,24 +1600,24 @@
         <v>20</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/WaveConfig.xlsx
+++ b/Unity/Assets/Config/Excel/WaveConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="60">
   <si>
     <t>##var</t>
   </si>
@@ -92,7 +92,7 @@
     <t>0,0</t>
   </si>
   <si>
-    <t>2;-5,50;10000001@2;5,50;10000002@2;0,50;10000002@2.2;5,50;10000002@2.2;2,50;10000002@2.4;2,50;10000002</t>
+    <t>0.5;-5,50;10000001@2.5;5,50;10000002</t>
   </si>
   <si>
     <t>关卡1-1第2波</t>
@@ -135,9 +135,6 @@
   </si>
   <si>
     <t>关卡1-2第1波</t>
-  </si>
-  <si>
-    <t>0.5;-5,50;10000001@2.5;5,50;10000002</t>
   </si>
   <si>
     <t>10202</t>
@@ -1430,15 +1427,15 @@
         <v>20</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="2:6">
       <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>19</v>
@@ -1447,15 +1444,15 @@
         <v>20</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="2:6">
       <c r="B12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>19</v>
@@ -1464,15 +1461,15 @@
         <v>20</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="2:6">
       <c r="B13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>19</v>
@@ -1481,15 +1478,15 @@
         <v>20</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="2:6">
       <c r="B14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>19</v>
@@ -1498,15 +1495,15 @@
         <v>20</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="2:6">
       <c r="B15" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>31</v>
@@ -1515,15 +1512,15 @@
         <v>32</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="2:6">
       <c r="B16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>19</v>
@@ -1532,15 +1529,15 @@
         <v>20</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="2:6">
       <c r="B17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>19</v>
@@ -1549,15 +1546,15 @@
         <v>20</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="2:6">
       <c r="B18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>19</v>
@@ -1566,15 +1563,15 @@
         <v>20</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="2:6">
       <c r="B19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>19</v>
@@ -1583,15 +1580,15 @@
         <v>20</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:6">
       <c r="B20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>19</v>
@@ -1600,15 +1597,15 @@
         <v>20</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="2:6">
       <c r="B21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>31</v>
